--- a/법령_개정안_안내/database/법규리스트.xlsx
+++ b/법령_개정안_안내/database/법규리스트.xlsx
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20260519</v>
+        <v>20260910</v>
       </c>
       <c r="C3" t="n">
-        <v>20260519</v>
+        <v>20260910</v>
       </c>
     </row>
     <row r="4">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20250510</v>
+        <v>20260929</v>
       </c>
       <c r="C20" t="n">
-        <v>20181224</v>
+        <v>20260929</v>
       </c>
     </row>
     <row r="21">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20260708</v>
+        <v>20260909</v>
       </c>
       <c r="C25" t="n">
-        <v>20260708</v>
+        <v>20260909</v>
       </c>
     </row>
     <row r="26">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>20260908</v>
+        <v>20260929</v>
       </c>
       <c r="C39" t="n">
-        <v>20260908</v>
+        <v>20260929</v>
       </c>
     </row>
     <row r="40">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>20250510</v>
+        <v>20260929</v>
       </c>
       <c r="C41" t="n">
-        <v>20230711</v>
+        <v>20260929</v>
       </c>
     </row>
     <row r="42">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>20251230</v>
+        <v>20260929</v>
       </c>
       <c r="C47" t="n">
-        <v>20251230</v>
+        <v>20260929</v>
       </c>
     </row>
     <row r="48">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>20260702</v>
+        <v>20260916</v>
       </c>
       <c r="C76" t="n">
-        <v>20260702</v>
+        <v>20260916</v>
       </c>
     </row>
     <row r="77">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>20260331</v>
+        <v>20260929</v>
       </c>
       <c r="C89" t="n">
-        <v>20260331</v>
+        <v>20260929</v>
       </c>
     </row>
     <row r="90">
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>20251216</v>
+        <v>20260929</v>
       </c>
       <c r="C116" t="n">
-        <v>20251216</v>
+        <v>20260929</v>
       </c>
     </row>
     <row r="117">
